--- a/outputs/Block5_Senate_Distribution.xlsx
+++ b/outputs/Block5_Senate_Distribution.xlsx
@@ -453,13 +453,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.310958350932499</v>
+        <v>0.3280263093622507</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -481,13 +481,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1.234402433809649</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>-0.06279383028951013</v>
+        <v>0.02733734900811324</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -495,13 +495,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.3293773794100608</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>-0.2835868085528425</v>
+        <v>-0.2767323416308665</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -509,13 +509,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1.430889012604439</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>-0.2319645301829925</v>
+        <v>-0.2994861004866491</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -537,13 +537,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="C8">
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.3255473089984537</v>
+        <v>0.2208547837471517</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -551,13 +551,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>0.06755162617559574</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>-0.05816049090560802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -565,13 +565,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0.2119323948670038</v>
+        <v>0.2197022323415841</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -579,13 +579,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.2515386496910184</v>
+        <v>0.1343074487636272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -599,7 +599,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>-0.141286249557361</v>
+        <v>-0.1495117733786751</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -607,13 +607,13 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>-0.09660377005771714</v>
+        <v>-0.1421544180751302</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -621,13 +621,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>-0.009975999869360042</v>
+        <v>-0.04660986031690806</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -635,13 +635,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>-0.3085361649247209</v>
+        <v>-0.3618566504167141</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -649,13 +649,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>-0.158607509839884</v>
+        <v>0.2118155723185868</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -663,13 +663,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>0.2515386496910184</v>
+        <v>0.1343074487636272</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5_Senate_Distribution.xlsx
+++ b/outputs/Block5_Senate_Distribution.xlsx
@@ -453,13 +453,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.7868170324027036</v>
+        <v>0.8817836191054232</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.3280263093622507</v>
+        <v>0.3063593944164298</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -481,13 +481,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1.138895095514905</v>
+        <v>0.883771840094469</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0.02733734900811324</v>
+        <v>0.3047953930208552</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -495,13 +495,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.3240271499397565</v>
+        <v>0.7561917677339507</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>-0.2767323416308665</v>
+        <v>0.4051541621510011</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -509,13 +509,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1.52157415011752</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>-0.2994861004866491</v>
+        <v>-0.2652426854826757</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -523,13 +523,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-0.1953923886052483</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -537,13 +537,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>11.45044534583586</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>0.2208547837471517</v>
+        <v>-0.5556738755003625</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -565,13 +565,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0.6788079824227848</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0.2197022323415841</v>
+        <v>0.2240162088952179</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -579,13 +579,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.7530958545051754</v>
+        <v>0.8641642373275472</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.1343074487636272</v>
+        <v>-0.06488243057422394</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -599,7 +599,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>-0.1495117733786751</v>
+        <v>-0.2322685718485682</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -607,13 +607,13 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>0.9935995824715044</v>
+        <v>1.059965154885961</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>-0.1421544180751302</v>
+        <v>-0.3061617476205698</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -621,13 +621,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>1.780416614874208</v>
+        <v>1.941748773991384</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>-0.04660986031690806</v>
+        <v>-0.3927559886150713</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -635,13 +635,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>0.3147916000487194</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>-0.3618566504167141</v>
+        <v>0.4698220434842124</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -649,13 +649,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>12.86475247157808</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16">
-        <v>0.2118155723185868</v>
+        <v>0.3671129168532268</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -663,13 +663,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>0.7530958545051754</v>
+        <v>0.8641642373275472</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>0.1343074487636272</v>
+        <v>-0.06488243057422394</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5_Senate_Distribution.xlsx
+++ b/outputs/Block5_Senate_Distribution.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dd0af9f211044926f193d3ea436dabde2b2960f060ab768c53232e3e59f37c10</t>
+          <t>69084551907b520052181adf33e09563f086f0b6de4f1d95d2e192b06c14159d</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T02:41:23.457320+00:00</t>
+          <t>2026-10-24T07:22:07.989106+00:00</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20T06:09:32.147340+00:00</t>
+          <t>2026-10-24T07:24:45.840036+00:00</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20T06:11:56.240312+00:00</t>
+          <t>2026-10-24T07:26:59.123079+00:00</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>35-race structural motor + polling enrichment on 12 monitored races</t>
+          <t>35-race structural motor + polling enrichment on 15 monitored races</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,53 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public Senate map highlights 12 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+          <t>Public Senate map highlights 15 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration source</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recovered Model(5).xlsx / Senate Historic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration rows</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration reference SHA256</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7b3f807a5128485c7fd4de43f99733784af9627e835db4777c047b68e762feb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senate production policy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recovered 5B calibration + 15 current monitored races; automatic structural blending disabled</t>
         </is>
       </c>
     </row>
@@ -896,7 +942,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -920,7 +966,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6254f3f54af6754b67deae4c4b8445dd2c4a92fbbcded33cef106f4df9255f2a</t>
+          <t>8a7bfde9efafe267b78417530287877a5e160939951e8ae39d62138f60d4e05a</t>
         </is>
       </c>
     </row>
@@ -932,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T06:12:00.987520+00:00</t>
+          <t>2026-10-24T07:27:04.098692+00:00</t>
         </is>
       </c>
     </row>
